--- a/teach/alunos/Jelson Vunda/dados_comerciais_angola.xlsx
+++ b/teach/alunos/Jelson Vunda/dados_comerciais_angola.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Documents\Aniceto\Teach\Excel\0000\Aula\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aula\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5484CD4-19EC-4F99-9F6C-039655A9D2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Encomendas" sheetId="1" r:id="rId1"/>
     <sheet name="Faturas" sheetId="2" r:id="rId2"/>
     <sheet name="Reuniões" sheetId="3" r:id="rId3"/>
+    <sheet name="Exercícios" sheetId="5" r:id="rId4"/>
+    <sheet name="Outros" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -4104,10 +4105,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$Kz]_-;\-* #,##0.00\ [$Kz]_-;_-* &quot;-&quot;??\ [$Kz]_-;_-@_-" x16r2:formatCode16="_-* #,##0.00\ [$Kz-pt-AO]_-;\-* #,##0.00\ [$Kz-pt-AO]_-;_-* &quot;-&quot;??\ [$Kz-pt-AO]_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="h:mm;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$Kz]_-;\-* #,##0.00\ [$Kz]_-;_-* &quot;-&quot;??\ [$Kz]_-;_-@_-" x16r2:formatCode16="_-* #,##0.00\ [$Kz-pt-AO]_-;\-* #,##0.00\ [$Kz-pt-AO]_-;_-* &quot;-&quot;??\ [$Kz-pt-AO]_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -4172,18 +4173,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4196,10 +4197,10 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="h:mm;@"/>
+      <numFmt numFmtId="165" formatCode="h:mm;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -4209,6 +4210,20 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4224,7 +4239,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4240,11 +4254,22 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$Kz]_-;\-* #,##0.00\ [$Kz]_-;_-* &quot;-&quot;??\ [$Kz]_-;_-@_-" x16r2:formatCode16="_-* #,##0.00\ [$Kz-pt-AO]_-;\-* #,##0.00\ [$Kz-pt-AO]_-;_-* &quot;-&quot;??\ [$Kz-pt-AO]_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -4254,22 +4279,11 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$Kz]_-;\-* #,##0.00\ [$Kz]_-;_-* &quot;-&quot;??\ [$Kz]_-;_-@_-" x16r2:formatCode16="_-* #,##0.00\ [$Kz-pt-AO]_-;\-* #,##0.00\ [$Kz-pt-AO]_-;_-* &quot;-&quot;??\ [$Kz-pt-AO]_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4285,7 +4299,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4301,27 +4314,13 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$Kz]_-;\-* #,##0.00\ [$Kz]_-;_-* &quot;-&quot;??\ [$Kz]_-;_-@_-" x16r2:formatCode16="_-* #,##0.00\ [$Kz-pt-AO]_-;\-* #,##0.00\ [$Kz-pt-AO]_-;_-* &quot;-&quot;??\ [$Kz-pt-AO]_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$Kz]_-;\-* #,##0.00\ [$Kz]_-;_-* &quot;-&quot;??\ [$Kz]_-;_-@_-" x16r2:formatCode16="_-* #,##0.00\ [$Kz-pt-AO]_-;\-* #,##0.00\ [$Kz-pt-AO]_-;_-* &quot;-&quot;??\ [$Kz-pt-AO]_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -4334,6 +4333,20 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4349,7 +4362,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4362,20 +4374,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
       </border>
     </dxf>
   </dxfs>
@@ -4403,8 +4401,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>255673</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>79978</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>67235</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4419,8 +4417,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7199399" y="118078"/>
-          <a:ext cx="5522118" cy="3009900"/>
+          <a:off x="7224612" y="118078"/>
+          <a:ext cx="5503208" cy="2616157"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4456,7 +4454,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
-            <a:t>Analises:</a:t>
+            <a:t>Analises 1:</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4609,7 +4607,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
-            <a:t> da coluno dos clientes da planilha </a:t>
+            <a:t> da coluna dos clientes da planilha </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="pt-PT" sz="1100" b="1" baseline="0"/>
@@ -4632,6 +4630,4225 @@
             <a:t>- gerar um grafico de linha</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+            <a:t>5-Na planilha Faturas fazer a limpeza de dados da coluna </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1100" b="1" baseline="0"/>
+            <a:t>Cliente</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+            <a:t> e depois gera o </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1100" b="1" baseline="0"/>
+            <a:t>valor</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+            <a:t>de cada cliente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>205248</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>124802</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>262397</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7253748" y="2791802"/>
+          <a:ext cx="5573366" cy="6072051"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Analises 2:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1. Análises por cliente</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Valor total vendido por cliente</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (tab. Encomendas):</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Usar SOMASE para somar o “Valor (Kz)” por cliente e criar um pequeno “dashboard” de faturamento por cliente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Quantidade total por cliente</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SOMASE em “Quantidade” por cliente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Cliente com maior valor total vendido</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SOMA em conjunto com SE/MÁXIMO ou ÍNDICE(CORRESP(MÁXIMO(...))) para retornar o nome do cliente com maior valor total.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Percentual do total geral por cliente</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>divisão do valor do cliente pelo total geral, usando referências absolutas ($).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2. Análises por produto e estado</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Valor total por produto</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ex.: papel A4, cimento, tinta, cadeiras, mesas, etc.):</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SOMASE com critério “Produto”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Quantidade e valor por produto + estado</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (EX: “luzes em trânsito” vs “luzes entregues”):</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>usar SOMASE com SE encadeado ou depois passar para SOMASES como desafio extra.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Produto mais vendido em quantidade</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>MÁXIMO + ÍNDICE(CORRESP()) para retornar o nome do produto com maior quantidade.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Valor médio por pedido por produto</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SOMA(Valor) / CONT.SE quantidade de pedidos do produto.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3. PROCV entre tabelas</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- “Buscar valor da fatura por Nº Fatura”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Criar uma tabela de busca com PROCV (ou ÍNDICE+CORRESP) para trazer o valor, data de vencimento ou estado de uma fatura a partir de um número digitado.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- “Buscar encomenda por Nº Encomenda”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>tabela de dados de encomenda com ÍNDICE(CORRESP(...)) para retornar Cliente, Produto, Quantidade, Valor e Estado de uma encomenda específica.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Relacionar Cliente ↔ Faturas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>usar PROCV ou ÍNDICE(CORRESP) para, a partir de um cliente, trazer o valor da última fatura ou o número da fatura.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>609676</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>183137</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>54503</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CaixaDeTexto 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13254114" y="183137"/>
+          <a:ext cx="5636077" cy="4412676"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Analises 3:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4. Análises de prazos e datas</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-Dias em atraso da fatura</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SE para comparar “Data Vencimento” com a data de hoje e calcular dias em atraso quando o estado for “Em atraso”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Total de faturas em atraso</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SOMASE com critério “Estado = Em atraso” no valor, ou SOMARPRODUTO como desafio.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Total de faturas pagas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SOMASE com “Estado = Pago”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Média de valor por estado</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>combinar SOMA e CONT.SE para cada estado e calcular a média.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>5. Análises por reuniões</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Quantidade de reuniões por empresa</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CONT.SE por “Empresa” na tabela de reuniões.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Valor total faturado por empresa com reunião</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>cruzar “Empresa” da reunião com “Cliente” das encomendas/faturas usando PROCV ou ÍNDICE+CORRESP para associar e depois somar.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Empresa com mais reuniões</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>MÁXIMO sobre a coluna de contagens de reunião por empresa + ÍNDICE(CORRESP()) para retornar o nome.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Reunião marcada na semana</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>usar SE com critérios de data (ex.: SE(Data&gt;=data_inicio; SE(Data&lt;=data_fim; "Sim"; ""); "")).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>25976</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CaixaDeTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5512376" cy="2257425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Exercício 1:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1. Exercícios combinando lógica condicional</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Classificar encomenda por valor</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>criar uma coluna com SE para categorizar encomenda em “Baixo”, “Médio”, “Alto” conforme critério de valor (ex.: &lt;10M, 10–30M, &gt;30M).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Classificar cliente por volume</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>somar valor total por cliente com SOMASE e depois usar SE encadeado para classificar “Pequeno”, “Médio”, “Grande”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Indicar se encomenda está em risco</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SE para verificar se Estado = Pendente e Data Pedido for de meses atrás, ou se Data Pedido for recente e Estado = Em trânsito.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="CaixaDeTexto 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5734049" y="1"/>
+          <a:ext cx="6715126" cy="2590800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Exercício 2:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>7. Exercícios de “tabela de resumo”</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Pede ao aluno para montar, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>sem usar tabelas dinâmicas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (só fórmulas):</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tabela 1 – Faturamento por cliente</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>colunas: Cliente, Total Valor, Quantidade Total, Nº de encomendas.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tabela 2 – Por produto</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Produto, Total Quantidade, Total Valor, % sobre total geral.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tabela 3 – Por estado da encomenda</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Estado, Nº de encomendas, Total Valor.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tabela 4 – Faturas por estado</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Estado, Nº de faturas, Total Valor, Média de valor.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Nessas tabelas, usarás SOMASE, CONT.SE e ÍNDICE(CORRESP) para montar um relatório tipo “dashboard”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>349826</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CaixaDeTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6924675" y="9526"/>
+          <a:ext cx="5617151" cy="2743200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Exercício 1:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercícios com PROCH</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 1:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Crie uma linha de cabeçalho com os nomes de 5 clientes (ex.: BAI, Candando, ENSA, Sonangol, Refriango).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Abaixo, numa linha, calcule o valor total de encomendas para cada cliente usando SOMASE.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em outra célula, ao digitar um cliente, use PROCH para retornar o valor total desse cliente da linha de totais.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 2:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Crie uma linha com os produtos mais vendidos (Papel A4, Cimento, Lâmpadas, Mesas, Cadeiras).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Abaixo, use SOMASE para o total de valor por produto.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Depois, use PROCH para, digitando o nome de um produto numa célula, buscar o valor total correspondente na linha de totais.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>139657</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6715124" cy="2616157"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Analises 1:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1. Análises possíveis com PROCH</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Tabela de “indicadores resumidos” em linha</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Criar uma linha com:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>“Cliente” | “Total Valor” | “Nº de Encomendas” | “Total Faturas”</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>e usar PROCH("Cliente"; linha_de_nomes; linha_de_valores; FALSO) para buscar valores de cada cliente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Resumo por produto em linha</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Uma linha com produtos (Papel A4, Cimento, Tinta, etc.) e outra linha com valores totais; usar PROCH para trazer automaticamente o total de um produto escolhido.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Cruzamento com faturas pagas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Linha com “Clientes” e outra linha com “Valor total de faturas pagas”; usar PROCH para, digitando um cliente, retornar o total de faturas pagas desse cliente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>63457</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CaixaDeTexto 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2781300"/>
+          <a:ext cx="6715124" cy="2616157"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Analises 2:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2. Análise com PROC (PROCV simplificado)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> é uma função antiga de busca que funciona como PROCV ou PROCH, dependendo da orientação dos dados, mas é menos flexível e hoje é mais usada por compatibilidade.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="1" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Busca simples em tabela vertical ordenada</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ex.: tabela de clientes já ordenada por nome):</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>usar PROC(valor_procurado; coluna_de_busca; coluna_de_retorno) para retornar o valor mais recente abaixo (se for ordenada).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Busca em tabela horizontal</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ex.: meses na linha 1 e valores na linha 2):</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>usar PROC(valor_procurado; linha_de_busca; linha_de_retorno) para retornar o valor de um mês.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="CaixaDeTexto 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6886574" y="2819401"/>
+          <a:ext cx="5905501" cy="2743200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Exercício 2:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercícios com PROC</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 1:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Ordene a tabela de encomendas por </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cliente</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> em ordem alfabética.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Crie uma fórmula usando PROC para buscar o </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>valor</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> de uma encomenda dado o </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>número de encomenda</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> e retornar o valor.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Explique ao aluno que, se os dados não estiverem ordenados, o PROC pode não funcionar corretamente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 2 (tabela horizontal):</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Crie uma tabela em linha com:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>“Mês” | “Jan” | “Fev” | “Mar” | ... até “Dez”</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Abaixo, uma linha com “Total de faturas” por mês (pode ser simulado com valores simples).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use PROC("Mês Desejado"; 1ª linha; 2ª linha) para retornar o total de faturas de um mês.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="CaixaDeTexto 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5715000"/>
+          <a:ext cx="6715124" cy="2828925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Analises 3:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3. Análise com PROCURAR / LOCALIZAR</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROCURAR() ou LOCALIZAR() servem para </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>achar a posição de um texto dentro de uma célula</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ex.: onde aparece a palavra “Cimento” dentro da descrição).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Análises possíveis com PROCURAR / LOCALIZAR</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Identificar se um produto contém palavra-chave</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ex.: SE(PROCURAR("Lâmpadas"; A2)&gt;0; "Luz"; "Outro") para classificar o tipo de produto.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Separar produtos por categoria</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>usar PROCURAR para identificar se o nome do produto contém “Mesas”, “Cadeiras”, “Lâmpadas”, etc., e criar uma nova coluna de categoria.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Validar dados de texto</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>verificar se o campo Produto contém uma palavra esperada (ex.: “Cimento” deve aparecer em todas as linhas de cimento).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0AD7597-3FE7-7CDC-9F3E-98FE79746DAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6953249" y="5876925"/>
+          <a:ext cx="5905501" cy="8077200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-PT" sz="1600" b="1" u="sng"/>
+            <a:t>Exercício 3:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercícios com PROCURAR</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 1:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Crie uma nova coluna chamada “Categoria”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use PROCURAR combinado com SE para classificar:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Se o produto contém “Papel”, categoria = “Papel”;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Se contém “Cimento”, categoria = “Cimento”;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Se contém “Lâmpadas”, categoria = “Iluminação”;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Se não, categoria = “Outro”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 2:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Crie uma fórmula que retorne </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SIM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> se o Produto contém a palavra “Bebidas”, e </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>NÃO</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> caso contrário.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use SE(ÉERRO(PROCURAR("Bebidas"; A2)); "NÃO"; "SIM") para tratar o erro quando a palavra não existe.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4. Exercícios práticos unindo PROCV, PROCH, PROC, PROCURAR</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>mistura funções</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> em um único relatório. Exemplo:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 3 – Tabela de busca interativa</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em uma aba “Dashboard”:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Célula A1: “Digite o Nº Encomenda”</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Células abaixo: Cliente, Produto, Quantidade, Valor, Estado</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROCV</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> para buscar esses dados na tabela de Encomendas.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em outra região, use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROCH</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> para, digitando um </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cliente</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, retornar o </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>valor total de encomendas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> desse cliente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em outra ancora, use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> para buscar o </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>valor de uma fatura</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> dado o </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Nº Fatura</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (se a tabela estiver ordenada).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em outra coluna, use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROCURAR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> para classificar o Produto como “Papel”, “Cimento”, etc.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 4 – Relatório de clientes importantes</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Calcule:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Total de encomendas por cliente (SOMASE).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Total de faturas por cliente (SOMASE).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em outra coluna, use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROCV</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> para trazer o Cliente ao digitar o Nº Encomenda.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em outra, use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROCH</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> para, em uma tabela de resumo horizontal, trazer o valor total correspondente ao cliente.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Em outra, use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PROCURAR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> para classificar se o Cliente é “Grande” (se nome contém “BAI” ou “Sonangol”) ou “Outro”.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="3"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Exercício 5 – Busca Vertical e Horizontal</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
+          <a:endParaRPr lang="pt-PT" sz="1100" b="0" baseline="0"/>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -4640,56 +8857,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2215B322-58C5-43CC-8D98-5A2949E50BDD}" name="Tabela1" displayName="Tabela1" ref="A1:G301" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="28">
-  <autoFilter ref="A1:G301" xr:uid="{2215B322-58C5-43CC-8D98-5A2949E50BDD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:G301" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="27" tableBorderDxfId="26">
+  <autoFilter ref="A1:G301"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{969D2D9A-5B52-42D6-8474-8404A1A17D07}" name="Nº Encomenda" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{148C1A83-EF65-442B-9547-F79C04CE7553}" name="Cliente" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{04F524B4-8118-4CE6-8CCB-A3F2EC0DD97F}" name="Produto" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{DE05F528-AAD8-41E4-BBEC-B79A0CBF7766}" name="Quantidade" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{85F56EE6-C1F0-4B78-B9BA-528B8F4877C7}" name="Valor (Kz)" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{4368C609-6DF0-490E-A8E1-A06218BEA4E4}" name="Data Pedido" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{F11BBA0F-B699-464D-89F1-E5ED2FCA2527}" name="Estado" dataDxfId="19"/>
+    <tableColumn id="1" name="Nº Encomenda" dataDxfId="25"/>
+    <tableColumn id="2" name="Cliente" dataDxfId="24"/>
+    <tableColumn id="3" name="Produto" dataDxfId="23"/>
+    <tableColumn id="4" name="Quantidade" dataDxfId="22"/>
+    <tableColumn id="5" name="Valor (Kz)" dataDxfId="21"/>
+    <tableColumn id="6" name="Data Pedido" dataDxfId="20"/>
+    <tableColumn id="7" name="Estado" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9A0BA66-D058-4561-8368-6D516341C4C6}" name="Tabela2" displayName="Tabela2" ref="A1:F301" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="18">
-  <autoFilter ref="A1:F301" xr:uid="{A9A0BA66-D058-4561-8368-6D516341C4C6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela2" displayName="Tabela2" ref="A1:F301" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:F301"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{ED180CC8-B092-4B3D-B7D9-96E01E7A4D38}" name="Nº Fatura" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{AA0631F6-C955-41AF-B78C-F6E1034D4249}" name="Cliente" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{D97E72EF-A6BE-46AD-B00C-EA7F46A6E910}" name="Valor (Kz)" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{E15C2EDA-B21A-4AC9-9BD8-CEA257E4792F}" name="Data Emissão" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{753BB680-64C3-4447-9ADD-CB065102334C}" name="Data Vencimento" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{7DD60D91-395F-45CA-BD8C-154520A8A38C}" name="Estado" dataDxfId="10"/>
+    <tableColumn id="1" name="Nº Fatura" dataDxfId="15"/>
+    <tableColumn id="2" name="Cliente" dataDxfId="14"/>
+    <tableColumn id="3" name="Valor (Kz)" dataDxfId="13"/>
+    <tableColumn id="4" name="Data Emissão" dataDxfId="12"/>
+    <tableColumn id="5" name="Data Vencimento" dataDxfId="11"/>
+    <tableColumn id="6" name="Estado" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B752D6EA-3692-49DF-96EE-0C473ACDBF34}" name="Tabela3" displayName="Tabela3" ref="A1:G301" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="9">
-  <autoFilter ref="A1:G301" xr:uid="{B752D6EA-3692-49DF-96EE-0C473ACDBF34}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela3" displayName="Tabela3" ref="A1:G301" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
+  <autoFilter ref="A1:G301"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{72FEF0A4-2B43-41BB-89BD-7AD2F5BDED62}" name="Nº Reunião" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{D33DC1D2-AABD-4962-BDBD-808DEF8BF678}" name="Empresa" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{2066FF85-865C-43D0-8F6D-E696749094FC}" name="Assunto" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{86EBC243-2040-4275-BBF8-A8CF7F02ED29}" name="Data" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{5504537D-4DDE-4F59-843F-2B8FD0E0C8CE}" name="Hora" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{1F5B4BFB-F87A-4036-99BC-41B1E8E96CC8}" name="Local" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{F92227BB-5329-4682-AFF4-E0B7BF655FD8}" name="Responsável" dataDxfId="0"/>
+    <tableColumn id="1" name="Nº Reunião" dataDxfId="6"/>
+    <tableColumn id="2" name="Empresa" dataDxfId="5"/>
+    <tableColumn id="3" name="Assunto" dataDxfId="4"/>
+    <tableColumn id="4" name="Data" dataDxfId="3"/>
+    <tableColumn id="5" name="Hora" dataDxfId="2"/>
+    <tableColumn id="6" name="Local" dataDxfId="1"/>
+    <tableColumn id="7" name="Responsável" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4727,9 +8944,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4764,7 +8981,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4799,7 +9016,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4972,7 +9189,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4980,7 +9197,7 @@
     <col min="2" max="2" width="12" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
@@ -11918,7 +16135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17959,7 +22176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24901,4 +29118,25 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>